--- a/VerveStacks_NGA/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_NGA/SuppXLS/Scen_Base_VS.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F85116EE-FC4C-4715-B996-8E8726DB0C29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0FF507AC-11B0-467C-BB49-150B7E6F41BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Veda" sheetId="1" r:id="rId1"/>
-    <sheet name="re_targets" sheetId="5" r:id="rId2"/>
+    <sheet name="re_targets" sheetId="5" r:id="rId1"/>
+    <sheet name="Veda" sheetId="1" r:id="rId2"/>
     <sheet name="buildrates" sheetId="4" r:id="rId3"/>
     <sheet name="historical_data_long" sheetId="3" r:id="rId4"/>
   </sheets>
@@ -124,7 +124,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1372" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1374" uniqueCount="118">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -385,6 +385,9 @@
   </si>
   <si>
     <t>\I: hydro</t>
+  </si>
+  <si>
+    <t>UCE_min oil fleet utilization</t>
   </si>
   <si>
     <t>windon</t>
@@ -486,8 +489,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -615,7 +619,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -628,6 +632,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="4"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -969,6 +974,266 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CC2F70F-E56A-4BA4-974C-F18E22647002}">
+  <dimension ref="B9:L16"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B10" t="s">
+        <v>90</v>
+      </c>
+      <c r="C10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E10" t="s">
+        <v>93</v>
+      </c>
+      <c r="F10" t="s">
+        <v>94</v>
+      </c>
+      <c r="G10" t="s">
+        <v>95</v>
+      </c>
+      <c r="H10" t="s">
+        <v>96</v>
+      </c>
+      <c r="I10" t="s">
+        <v>97</v>
+      </c>
+      <c r="J10" t="s">
+        <v>98</v>
+      </c>
+      <c r="K10" t="s">
+        <v>99</v>
+      </c>
+      <c r="L10" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B11">
+        <v>2030</v>
+      </c>
+      <c r="C11" t="s">
+        <v>101</v>
+      </c>
+      <c r="D11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E11">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F11" t="s">
+        <v>103</v>
+      </c>
+      <c r="G11" t="s">
+        <v>104</v>
+      </c>
+      <c r="H11" t="s">
+        <v>105</v>
+      </c>
+      <c r="I11" s="13">
+        <v>42565</v>
+      </c>
+      <c r="J11" t="s">
+        <v>106</v>
+      </c>
+      <c r="K11" t="s">
+        <v>107</v>
+      </c>
+      <c r="L11" s="14" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B12">
+        <v>2030</v>
+      </c>
+      <c r="C12" t="s">
+        <v>109</v>
+      </c>
+      <c r="D12" t="s">
+        <v>102</v>
+      </c>
+      <c r="E12">
+        <v>5.9</v>
+      </c>
+      <c r="F12" t="s">
+        <v>103</v>
+      </c>
+      <c r="G12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H12" t="s">
+        <v>105</v>
+      </c>
+      <c r="I12" s="13">
+        <v>42565</v>
+      </c>
+      <c r="J12" t="s">
+        <v>106</v>
+      </c>
+      <c r="K12" t="s">
+        <v>107</v>
+      </c>
+      <c r="L12" s="14" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B13">
+        <v>2030</v>
+      </c>
+      <c r="C13" t="s">
+        <v>110</v>
+      </c>
+      <c r="D13" t="s">
+        <v>102</v>
+      </c>
+      <c r="E13">
+        <v>5.3739999999999997</v>
+      </c>
+      <c r="F13" t="s">
+        <v>103</v>
+      </c>
+      <c r="G13" t="s">
+        <v>104</v>
+      </c>
+      <c r="H13" t="s">
+        <v>105</v>
+      </c>
+      <c r="I13" s="13">
+        <v>42565</v>
+      </c>
+      <c r="J13" t="s">
+        <v>106</v>
+      </c>
+      <c r="K13" t="s">
+        <v>107</v>
+      </c>
+      <c r="L13" s="14" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B14">
+        <v>2030</v>
+      </c>
+      <c r="C14" t="s">
+        <v>111</v>
+      </c>
+      <c r="D14" t="s">
+        <v>102</v>
+      </c>
+      <c r="E14">
+        <v>6</v>
+      </c>
+      <c r="F14" t="s">
+        <v>103</v>
+      </c>
+      <c r="G14" t="s">
+        <v>104</v>
+      </c>
+      <c r="H14" t="s">
+        <v>105</v>
+      </c>
+      <c r="I14" s="13">
+        <v>42565</v>
+      </c>
+      <c r="J14" t="s">
+        <v>106</v>
+      </c>
+      <c r="K14" t="s">
+        <v>107</v>
+      </c>
+      <c r="L14" s="14" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B15">
+        <v>2030</v>
+      </c>
+      <c r="C15" t="s">
+        <v>112</v>
+      </c>
+      <c r="D15" t="s">
+        <v>102</v>
+      </c>
+      <c r="E15">
+        <v>0.8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>103</v>
+      </c>
+      <c r="G15" t="s">
+        <v>104</v>
+      </c>
+      <c r="H15" t="s">
+        <v>105</v>
+      </c>
+      <c r="I15" s="13">
+        <v>42565</v>
+      </c>
+      <c r="J15" t="s">
+        <v>106</v>
+      </c>
+      <c r="K15" t="s">
+        <v>107</v>
+      </c>
+      <c r="L15" s="14" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B16">
+        <v>2030</v>
+      </c>
+      <c r="C16" t="s">
+        <v>113</v>
+      </c>
+      <c r="D16" t="s">
+        <v>114</v>
+      </c>
+      <c r="E16">
+        <v>31</v>
+      </c>
+      <c r="F16" t="s">
+        <v>103</v>
+      </c>
+      <c r="G16" t="s">
+        <v>104</v>
+      </c>
+      <c r="H16" t="s">
+        <v>105</v>
+      </c>
+      <c r="I16" s="13">
+        <v>42565</v>
+      </c>
+      <c r="J16" t="s">
+        <v>106</v>
+      </c>
+      <c r="K16" t="s">
+        <v>107</v>
+      </c>
+      <c r="L16" s="14" t="s">
+        <v>108</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AL40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -999,7 +1264,7 @@
     <col min="33" max="33" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="7" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="7.86328125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="4.73046875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="5.265625" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="9.19921875" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="11.19921875" bestFit="1" customWidth="1"/>
   </cols>
@@ -1348,12 +1613,36 @@
     </row>
     <row r="10" spans="1:38" ht="14.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
+      <c r="AF10" t="s">
+        <v>87</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>23</v>
+      </c>
+      <c r="AH10">
+        <f>-1/8.76</f>
+        <v>-0.11415525114155252</v>
+      </c>
+      <c r="AI10" s="2">
+        <f>VLOOKUP(AG10,$F$3:$J$11,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="12">
+        <f>AI10*$AD$1</f>
+        <v>0</v>
+      </c>
+      <c r="AK10">
+        <v>0</v>
+      </c>
+      <c r="AL10">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:38" ht="14.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="G11" s="3"/>
@@ -1674,266 +1963,6 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04A5C71C-6EBF-459A-ABFE-F2D34A51428B}">
-  <dimension ref="B9:L16"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B9" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B10" t="s">
-        <v>89</v>
-      </c>
-      <c r="C10" t="s">
-        <v>90</v>
-      </c>
-      <c r="D10" t="s">
-        <v>91</v>
-      </c>
-      <c r="E10" t="s">
-        <v>92</v>
-      </c>
-      <c r="F10" t="s">
-        <v>93</v>
-      </c>
-      <c r="G10" t="s">
-        <v>94</v>
-      </c>
-      <c r="H10" t="s">
-        <v>95</v>
-      </c>
-      <c r="I10" t="s">
-        <v>96</v>
-      </c>
-      <c r="J10" t="s">
-        <v>97</v>
-      </c>
-      <c r="K10" t="s">
-        <v>98</v>
-      </c>
-      <c r="L10" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B11">
-        <v>2030</v>
-      </c>
-      <c r="C11" t="s">
-        <v>100</v>
-      </c>
-      <c r="D11" t="s">
-        <v>101</v>
-      </c>
-      <c r="E11">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="F11" t="s">
-        <v>102</v>
-      </c>
-      <c r="G11" t="s">
-        <v>103</v>
-      </c>
-      <c r="H11" t="s">
-        <v>104</v>
-      </c>
-      <c r="I11" s="12">
-        <v>42565</v>
-      </c>
-      <c r="J11" t="s">
-        <v>105</v>
-      </c>
-      <c r="K11" t="s">
-        <v>106</v>
-      </c>
-      <c r="L11" s="13" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B12">
-        <v>2030</v>
-      </c>
-      <c r="C12" t="s">
-        <v>108</v>
-      </c>
-      <c r="D12" t="s">
-        <v>101</v>
-      </c>
-      <c r="E12">
-        <v>5.9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>102</v>
-      </c>
-      <c r="G12" t="s">
-        <v>103</v>
-      </c>
-      <c r="H12" t="s">
-        <v>104</v>
-      </c>
-      <c r="I12" s="12">
-        <v>42565</v>
-      </c>
-      <c r="J12" t="s">
-        <v>105</v>
-      </c>
-      <c r="K12" t="s">
-        <v>106</v>
-      </c>
-      <c r="L12" s="13" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B13">
-        <v>2030</v>
-      </c>
-      <c r="C13" t="s">
-        <v>109</v>
-      </c>
-      <c r="D13" t="s">
-        <v>101</v>
-      </c>
-      <c r="E13">
-        <v>5.3739999999999997</v>
-      </c>
-      <c r="F13" t="s">
-        <v>102</v>
-      </c>
-      <c r="G13" t="s">
-        <v>103</v>
-      </c>
-      <c r="H13" t="s">
-        <v>104</v>
-      </c>
-      <c r="I13" s="12">
-        <v>42565</v>
-      </c>
-      <c r="J13" t="s">
-        <v>105</v>
-      </c>
-      <c r="K13" t="s">
-        <v>106</v>
-      </c>
-      <c r="L13" s="13" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B14">
-        <v>2030</v>
-      </c>
-      <c r="C14" t="s">
-        <v>110</v>
-      </c>
-      <c r="D14" t="s">
-        <v>101</v>
-      </c>
-      <c r="E14">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>102</v>
-      </c>
-      <c r="G14" t="s">
-        <v>103</v>
-      </c>
-      <c r="H14" t="s">
-        <v>104</v>
-      </c>
-      <c r="I14" s="12">
-        <v>42565</v>
-      </c>
-      <c r="J14" t="s">
-        <v>105</v>
-      </c>
-      <c r="K14" t="s">
-        <v>106</v>
-      </c>
-      <c r="L14" s="13" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B15">
-        <v>2030</v>
-      </c>
-      <c r="C15" t="s">
-        <v>111</v>
-      </c>
-      <c r="D15" t="s">
-        <v>101</v>
-      </c>
-      <c r="E15">
-        <v>0.8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>102</v>
-      </c>
-      <c r="G15" t="s">
-        <v>103</v>
-      </c>
-      <c r="H15" t="s">
-        <v>104</v>
-      </c>
-      <c r="I15" s="12">
-        <v>42565</v>
-      </c>
-      <c r="J15" t="s">
-        <v>105</v>
-      </c>
-      <c r="K15" t="s">
-        <v>106</v>
-      </c>
-      <c r="L15" s="13" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B16">
-        <v>2030</v>
-      </c>
-      <c r="C16" t="s">
-        <v>112</v>
-      </c>
-      <c r="D16" t="s">
-        <v>113</v>
-      </c>
-      <c r="E16">
-        <v>31</v>
-      </c>
-      <c r="F16" t="s">
-        <v>102</v>
-      </c>
-      <c r="G16" t="s">
-        <v>103</v>
-      </c>
-      <c r="H16" t="s">
-        <v>104</v>
-      </c>
-      <c r="I16" s="12">
-        <v>42565</v>
-      </c>
-      <c r="J16" t="s">
-        <v>105</v>
-      </c>
-      <c r="K16" t="s">
-        <v>106</v>
-      </c>
-      <c r="L16" s="13" t="s">
-        <v>107</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -1956,12 +1985,12 @@
   <sheetData>
     <row r="9" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C10" t="s">
         <v>68</v>
@@ -1990,7 +2019,7 @@
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C11">
         <v>8</v>
@@ -5527,7 +5556,7 @@
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A250" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B250">
         <v>2000</v>
@@ -5653,7 +5682,7 @@
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A259" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B259">
         <v>2001</v>
@@ -5779,7 +5808,7 @@
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A268" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B268">
         <v>2002</v>
@@ -5905,7 +5934,7 @@
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A277" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B277">
         <v>2003</v>
@@ -6031,7 +6060,7 @@
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A286" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B286">
         <v>2004</v>
@@ -6157,7 +6186,7 @@
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A295" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B295">
         <v>2005</v>
@@ -6283,7 +6312,7 @@
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A304" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B304">
         <v>2006</v>
@@ -6409,7 +6438,7 @@
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A313" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B313">
         <v>2007</v>
@@ -6535,7 +6564,7 @@
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A322" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B322">
         <v>2008</v>
@@ -6661,7 +6690,7 @@
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A331" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B331">
         <v>2009</v>
@@ -6787,7 +6816,7 @@
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A340" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B340">
         <v>2010</v>
@@ -6913,7 +6942,7 @@
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A349" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B349">
         <v>2011</v>
@@ -7039,7 +7068,7 @@
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A358" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B358">
         <v>2012</v>
@@ -7165,7 +7194,7 @@
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A367" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B367">
         <v>2013</v>
@@ -7291,7 +7320,7 @@
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A376" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B376">
         <v>2014</v>
@@ -7417,7 +7446,7 @@
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A385" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B385">
         <v>2015</v>
@@ -7543,7 +7572,7 @@
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A394" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B394">
         <v>2016</v>
@@ -7669,7 +7698,7 @@
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A403" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B403">
         <v>2017</v>
@@ -7795,7 +7824,7 @@
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A412" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B412">
         <v>2018</v>
@@ -7921,7 +7950,7 @@
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A421" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B421">
         <v>2019</v>
@@ -8047,7 +8076,7 @@
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A430" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B430">
         <v>2020</v>
@@ -8173,7 +8202,7 @@
     </row>
     <row r="439" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A439" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B439">
         <v>2021</v>
@@ -8299,7 +8328,7 @@
     </row>
     <row r="448" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A448" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B448">
         <v>2022</v>
@@ -8425,7 +8454,7 @@
     </row>
     <row r="457" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A457" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B457">
         <v>2023</v>
